--- a/docs/dss-matrix.xlsx
+++ b/docs/dss-matrix.xlsx
@@ -60,88 +60,88 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Screening</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>item_type/details.item_types</t>
+          <t>details.uniform_branding</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>What type of item/s are you submitting?</t>
+          <t>Donation only: uniform or identifiable company/school/institutional branding?</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Top; Pants/Jeans; Dress; Jacket; Household textile; Fabric scraps; Other</t>
+          <t>Yes blocks Donation and recommends Upcycle or Recycle; No continues</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>item_type/details.item_types</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Overall condition</t>
+          <t>What type of item/s are you submitting?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Good; Minor damage; Heavily damaged</t>
+          <t>Donation excludes Fabric scraps. Recycle/Upcycle: Top; Pants/Jeans; Dress; Jacket; Household textile; Fabric scraps; Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cleanliness</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>cleanliness</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Is/are the item/s clean?</t>
+          <t>Overall condition</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Clean; Needs cleaning; Heavily soiled/contaminated</t>
+          <t>Good; Minor damage; Heavily damaged</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Fabric</t>
+          <t>Cleanliness</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>details.knows_fabric_type</t>
+          <t>cleanliness</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Do you know the fabric type?</t>
+          <t>Is/are the item/s clean?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Yes; No</t>
+          <t>Donation blocks Heavily soiled/contaminated; other forms keep existing behavior</t>
         </is>
       </c>
     </row>
@@ -153,17 +153,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>details.fabric_types</t>
+          <t>details.knows_fabric_type</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What is the fabric type?</t>
+          <t>Do you know the fabric type?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Cotton/Linen; Polyester/nylon/acrylic; Viscose/Rayon; Blends; Coated/PPE; Wool/Silk; Other/user-defined</t>
+          <t>Yes; No</t>
         </is>
       </c>
     </row>
@@ -175,17 +175,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>details.custom_fabric_text</t>
+          <t>details.fabric_types</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>User-defined fabric text</t>
+          <t>What is the fabric type?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Free text</t>
+          <t>Cotton/Linen; Polyester/nylon/acrylic; Viscose/Rayon; Blends; Coated/PPE; Wool/Silk; Other/user-defined</t>
         </is>
       </c>
     </row>
@@ -197,37 +197,103 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>details.fiber_composition</t>
+          <t>details.custom_fabric_text</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Main material/fiber composition</t>
+          <t>User-defined fabric text</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Cotton/natural; Polyester/synthetic; Blend; Wool/silk/delicate; Mixed/unknown</t>
+          <t>Free text</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Fabric</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>details.fiber_composition</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Main material/fiber composition</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Cotton/natural; Polyester/synthetic; Blend; Wool/silk/delicate; Mixed/unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Recovery</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>details.wearability</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Is the item still wearable or usable?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Donation skips Recovery. Recycle/Upcycle disable and do not require/score when Fabric scraps is the only selected item type</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>details.repairability</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Is the item repairable?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Donation skips Recovery. Recycle/Upcycle disable and do not require/score when Fabric scraps is the only selected item type</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>details.contamination_level</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Contamination level</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Only if condition is minor/heavy damage</t>
         </is>
@@ -629,17 +695,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Wearability</t>
+          <t>Hard eligibility</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Wearable as-is or minor repair</t>
+          <t>Blocks uniforms/branded institutional clothing, heavily damaged items, heavily soiled/contaminated items, and Fabric scraps</t>
         </is>
       </c>
     </row>
@@ -651,17 +717,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cleanliness/contamination</t>
+          <t>Item choices</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Clean or washable only</t>
+          <t>Fabric scraps is removed from Donation item type choices</t>
         </is>
       </c>
     </row>
@@ -673,51 +739,51 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Damage/repair</t>
+          <t>Recovery Criteria</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>No damage or minor repairable damage</t>
+          <t>Donation form skips Recovery Criteria entirely</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Upcycle</t>
+          <t>Donation</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Repurposing potential</t>
+          <t>Wearability</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>High or medium</t>
+          <t>Wearable as-is or minor repair</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Upcycle</t>
+          <t>Donation</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Repairability/damage</t>
+          <t>Cleanliness/contamination</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -727,49 +793,137 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Repair/redesign can preserve material value</t>
+          <t>Clean or washable only</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Recycle</t>
+          <t>Donation</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fabric/material signal</t>
+          <t>Damage/repair</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Identifiable recyclable fiber/material</t>
+          <t>No damage or minor repairable damage</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>All applicable Recovery forms</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Fabric scraps-only skip</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Normalize</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>When only Fabric scraps is selected, Wearability and Repairability are disabled, cleared, not required, and excluded from scoring normalization</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Upcycle</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Repurposing potential</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>High or medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Upcycle</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Repairability/damage</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Repair/redesign can preserve material value</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Recycle</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Fabric/material signal</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Identifiable recyclable fiber/material</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Recycle</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>Damage/contamination/trim</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Material recovery fit without hazardous contamination</t>
         </is>
@@ -830,6 +984,30 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Donation uniform/branded clothing</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Block Donation only; store details.uniform_branding for DSS audit consistency</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Fabric scraps-only Recovery Criteria</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Disable Wearability and Repairability; submit null values and exclude their weights from scoring</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/docs/dss-matrix.xlsx
+++ b/docs/dss-matrix.xlsx
@@ -2,10 +2,10 @@
 <file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Intake Flow" sheetId="1" r:id="rId1"/>
-    <sheet name="Burn Test Logic" sheetId="2" r:id="rId2"/>
-    <sheet name="Pathway Scoring" sheetId="3" r:id="rId3"/>
-    <sheet name="Cleanup Notes" sheetId="4" r:id="rId4"/>
+    <sheet name="DSS Overview" sheetId="1" r:id="rId1"/>
+    <sheet name="Intake Fields" sheetId="2" r:id="rId2"/>
+    <sheet name="Burn Test Logic" sheetId="3" r:id="rId3"/>
+    <sheet name="Pathway Scoring" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -16,286 +16,170 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Area</t>
+          <t>Topic</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Field</t>
+          <t>Current behavior</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Question / Source</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Choices / Input</t>
+          <t>Source / notes</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Screening</t>
+          <t>Engine version</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>details.restricted_category</t>
+          <t>dssEngine-v2-textile-recovery</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Does the item belong to any restricted category?</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Hospital/medical uniform; PPE or contaminated workwear; Used undergarments; Mold/chemical contaminated; None</t>
+          <t>backend/src/services/dssEngine.ts</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Screening</t>
+          <t>Last updated</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>details.uniform_branding</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Donation only: uniform or identifiable company/school/institutional branding?</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Yes blocks Donation and recommends Upcycle or Recycle; No continues</t>
+          <t>Aligned with docs/dss-matrix.md</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Ranked DSS recommendations</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>item_type/details.item_types</t>
+          <t>Recycle, Donate, Upcycle</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>What type of item/s are you submitting?</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Donation excludes Fabric scraps. Recycle/Upcycle: Top; Pants/Jeans; Dress; Jacket; Household textile; Fabric scraps; Other</t>
+          <t>Only these three can be selected and sent to partners</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Rejected result</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>Hard-stop output for restricted/unsafe items</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Overall condition</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Good; Minor damage; Heavily damaged</t>
+          <t>Not sent as a partner request</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cleanliness</t>
+          <t>Buyback</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>cleanliness</t>
+          <t>Yes/No preference only</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Is/are the item/s clean?</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Donation blocks Heavily soiled/contaminated; other forms keep existing behavior</t>
+          <t>Not a DSS pathway score; appears when final selected pathway is Upcycle</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Fabric</t>
+          <t>Preference boost</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>details.knows_fabric_type</t>
+          <t>Selected service receives +8 points, capped at 100</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Do you know the fabric type?</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Yes; No</t>
+          <t>Applies to Recycle/Donate/Upcycle scores only</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Fabric</t>
+          <t>Admin editable rules</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>details.fabric_types</t>
+          <t>Saved for documentation/audit/future publishing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What is the fabric type?</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Cotton/Linen; Polyester/nylon/acrylic; Viscose/Rayon; Blends; Coated/PPE; Wool/Silk; Other/user-defined</t>
+          <t>Live DSS engine still uses coded rules</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Fabric</t>
+          <t>Partner brief</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>details.custom_fabric_text</t>
+          <t>Shows selected pathway, confidence, score, all pathway scores, checks, item details, burn-test result, and Upcycle buyback preference</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>User-defined fabric text</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Free text</t>
+          <t>Generated when user sends a DSS request</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fabric</t>
+          <t>Audit trail</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>details.fiber_composition</t>
+          <t>Saves recommendation_runs and selected recommendation_results</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Main material/fiber composition</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Cotton/natural; Polyester/synthetic; Blend; Wool/silk/delicate; Mixed/unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Recovery</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>details.wearability</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Is the item still wearable or usable?</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Donation skips Recovery. Recycle/Upcycle disable and do not require/score when Fabric scraps is the only selected item type</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Recovery</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>details.repairability</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Is the item repairable?</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Donation skips Recovery. Recycle/Upcycle disable and do not require/score when Fabric scraps is the only selected item type</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Recovery</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>details.contamination_level</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Contamination level</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Only if condition is minor/heavy damage</t>
+          <t>Includes engine_version, input snapshot, selected partner, selected pathway, score, confidence, and checks</t>
         </is>
       </c>
     </row>
@@ -309,352 +193,572 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Fiber</t>
+          <t>Area</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Moment</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Flames</t>
+          <t>Question / Source</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>No flame</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Smell</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Ashes</t>
+          <t>Choices / Input</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>cotton</t>
+          <t>Screening</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Burned fast</t>
+          <t>details.restricted_category</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Burns quickly</t>
+          <t>Does the item belong to any restricted category?</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Continues quickly, afterglow</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Burning paper</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Light gray ash OR black ash</t>
+          <t>Hospital/medical uniform; PPE or contaminated workwear; Used undergarments; Mold- or chemical-contaminated textile; None of the above</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>linen</t>
+          <t>Screening</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Burned fast</t>
+          <t>details.uniform_branding</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Burns quickly</t>
+          <t>Donation only: uniform or identifiable company/school/institutional branding?</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Continues to burn</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Burning paper</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Light gray ash</t>
+          <t>Yes blocks Donation and recommends Upcycle or Recycle; No continues</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>rayon/tencel</t>
+          <t>Submission label</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Burned fast</t>
+          <t>submission_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Burns quickly</t>
+          <t>Name this submission</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Continues quickly</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Burning paper</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Light gray ash</t>
+          <t>Free text</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>silk</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Curled away, no flame</t>
+          <t>item_type/details.item_types</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Burns slowly, sputters</t>
+          <t>What type of item/s are you submitting?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Burns with difficulty, stops</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Burning hair</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Shiny black beads and easy crush</t>
+          <t>Donation: Top; Bottoms; Outerwear. Recycle/Upcycle/general textile flow: Scraps; Big fabric panels (curtains, bedsheets); Clothes (top, outerwear, bottoms)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>wool</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Curled away, no flame, burned slowly</t>
+          <t>details.other_item_type</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Burns slowly, sizzles, flickering</t>
+          <t>Legacy other item type</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Stops burning</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Burning hair</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Easy to crush, irregular bead</t>
+          <t>Free text from older submissions only</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>nylon</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Melted and did not burn, shrinked away</t>
+          <t>condition/details.condition</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Melts, burns slowly</t>
+          <t>Overall condition</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Stops burning</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Celery</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Hard gray bead and will not crush</t>
+          <t>Good condition; Minor damage; Heavily damaged</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>polyester/poly fleece</t>
+          <t>Cleanliness</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Shrinked away</t>
+          <t>cleanliness/details.cleanliness</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Melts, burns slowly</t>
+          <t>Is/are the item/s clean?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Burns with difficulty</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Chemicals</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Hard gray bead and will not crush</t>
+          <t>Yes, clean and ready for use; Needs cleaning; Heavily soiled or contaminated</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>acetate</t>
+          <t>Quantity</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Shrinked away, turned black</t>
+          <t>quantity</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sputters, melts, drips, burns quickly</t>
+          <t>Quantity</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Continues to melt and burn</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Vinegar</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Hard black ash, irregular bead, difficult crush</t>
+          <t>Number; recycle prefers quantity &gt;= 2 or identifiable material</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>acrylic</t>
+          <t>Fabric</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Shrinked away</t>
+          <t>details.knows_fabric_type</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Burns quickly, sputters, melts</t>
+          <t>Do you know the fabric type?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Continues to melt and burn</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Chemicals</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Hard irregular black bead and will not crush</t>
+          <t>Yes; No</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>spandex</t>
+          <t>Fabric</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Shrinked away</t>
+          <t>details.fabric_types</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Melts, burns quickly</t>
+          <t>What is the fabric type?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Continues to melt and burn</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Sharp and bitter</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Soft sticky gummy</t>
+          <t>Cotton/Linen; Polyester/nylon/acrylic; Viscose/Rayon; Cotton-spandex/poly-spandex; Coated/PPE; Wool/Silk; Other/user-defined</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Fabric</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>details.custom_fabric_text</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>User-defined fabric text</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Free text when Other/user-defined is selected</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Fabric</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>details.fabric_identification</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>How did you identify the fabric?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Clothing label; Personal knowledge; Burn test</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Fabric</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>details.brand/details.no_brand_visible</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>What is the brand?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Free text; No brand visible</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Fabric</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>details.fabric_description</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>How would you describe the fabric?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Same descriptive fabric choices when type is unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fabric</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>details.fiber_composition</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Main material/fiber composition</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>100% cotton/natural; 100% polyester/synthetic; Cotton-poly/stretch blend; Wool/silk/delicate; Mixed/unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>details.wearability</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Is the item still wearable or usable?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Wearable as-is; Wearable after minor repair; Not wearable but fabric usable; Not usable. Disabled/not scored for scraps-only submissions</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>details.damage_classification</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Damage classification</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>No damage; Minor cosmetic issue; Missing button/loose seam; Small hole/tear; Large tear/heavy damage; Fabric degradation</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>details.repairability</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Is the item repairable?</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>No repair needed; Minor repair; Moderate repair; Not practical to repair. Disabled/not scored for scraps-only submissions</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>details.contamination_level</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Contamination level</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Appears only when condition is Minor damage or Heavily damaged. Clean; Washable dirt/odor; Permanent stain; Oil/paint/biological contamination; Chemical/mold contamination</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>details.repurposing_potential</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Repurposing potential</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>High; Medium; Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>details.trim_removal</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Are trims/accessories easy to remove?</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>None; Easy to remove; Difficult to remove; Many mixed components</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Pathway</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>service_type/action</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Intended pathway</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Donate; Recycle; Upcycle. DSS confirmation can later switch among these three</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Buyback</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>buyback_interest</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Interested in buyback?</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Yes; No. Only applies when final selected pathway is Upcycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Buyback</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>upcycle_request</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>What would you like this item to become?</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Free text shown when user says Yes to buyback during submission</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>photos[]</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Uploaded images</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>URL plus optional user label</t>
         </is>
       </c>
     </row>
@@ -668,264 +772,407 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Pathway</t>
+          <t>Fiber</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>Moment flame touched textile</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Weight</t>
+          <t>While in flames</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>After flame removed</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Smell</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Ash / residue</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Scoring note</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Donation</t>
+          <t>Cotton</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Hard eligibility</t>
+          <t>Burned fast</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Burns quickly</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Blocks uniforms/branded institutional clothing, heavily damaged items, heavily soiled/contaminated items, and Fabric scraps</t>
+          <t>Continues to burn quickly, Has an afterglow</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Like burning paper</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Light and feathery gray ash OR Black ash</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Backend splits OR groups and comma/&amp; tokens; partial tokens score partial credit</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Donation</t>
+          <t>Linen</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Item choices</t>
+          <t>Burned fast</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Burns quickly</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Fabric scraps is removed from Donation item type choices</t>
+          <t>Continues to burn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Like burning paper</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Light and feathery gray ash</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Full group match can reach 100%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Donation</t>
+          <t>Rayon / Tencel</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Recovery Criteria</t>
+          <t>Burned fast</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Burns quickly</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Donation form skips Recovery Criteria entirely</t>
+          <t>Continues to burn quickly</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Like burning paper</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Light and feathery gray ash</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Partial matches are capped at 92%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Donation</t>
+          <t>Silk</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wearability</t>
+          <t>Curled away, No flame</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>Burns slowly, Sputters</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Wearable as-is or minor repair</t>
+          <t>Burns with difficulty, Completely stops burning</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Like burning hair</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Round shiny black beads AND Easy to crush</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>AND-style ash evidence requires both tokens</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Donation</t>
+          <t>Wool</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cleanliness/contamination</t>
+          <t>Curled away, No flame, Burned slowly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>Burns slowly, Sizzles, Flame was flickering</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Clean or washable only</t>
+          <t>Completely stops burning</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Like burning hair</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Easy to crush, Irregular bead</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Example: selecting all three flame tokens gives 3/3 for that group</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Donation</t>
+          <t>Nylon</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Damage/repair</t>
+          <t>Melted and did not burn, Shrinked away from flame</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>Melts, Burns slowly</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>No damage or minor repairable damage</t>
+          <t>Completely stops burning</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Like celery</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Round hard grayish bead AND Will not crush</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Top 3 fibers are shown</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>All applicable Recovery forms</t>
+          <t>Polyester / Poly fleece</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Fabric scraps-only skip</t>
+          <t>Shrinked away from flame</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Normalize</t>
+          <t>Melts, Burns slowly</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>When only Fabric scraps is selected, Wearability and Repairability are disabled, cleared, not required, and excluded from scoring normalization</t>
+          <t>Burns with difficulty</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Like chemicals</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Round hard grayish bead AND Will not crush</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Used as fabric signal in pathway scoring</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Upcycle</t>
+          <t>Acetate</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Repurposing potential</t>
+          <t>Shrinked away from flame, Turned black</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>Sputters, Melts, Drips, Burns quickly</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>High or medium</t>
+          <t>Continues to melt and burn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Like vinegar</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Hard black ash, Irregular bead, Difficult to crush</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Synthetic/melting behavior supports recycling route</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Upcycle</t>
+          <t>Acrylic</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Repairability/damage</t>
+          <t>Shrinked away from flame</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>Burns quickly, Sputters, Melts</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Repair/redesign can preserve material value</t>
+          <t>Continues to melt and burn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Like chemicals</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Irregular hard black bead AND Will not crush</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Synthetic/melting behavior supports recycling route</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Recycle</t>
+          <t>Spandex</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fabric/material signal</t>
+          <t>Shrinked away from flame</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>Melts, Burns quickly</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Identifiable recyclable fiber/material</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Recycle</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Damage/contamination/trim</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Material recovery fit without hazardous contamination</t>
+          <t>Continues to melt and burn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sharp and bitter</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Soft, sticky, gummy</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Synthetic/stretch signal</t>
         </is>
       </c>
     </row>
@@ -939,72 +1186,968 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Pathway</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>Criterion</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Match condition</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>condition + wearability + damage + repairability</t>
+          <t>Eligibility gate</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Keep all, arranged as condition first then recovery detail</t>
+          <t>Restricted category</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Any restricted category except none returns Rejected with 100% confidence</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>cleanliness + contamination_level</t>
+          <t>Eligibility gate</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Keep both; contamination only appears for minor/heavy damage</t>
+          <t>Chemical/mold contamination</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Chemical or mold contamination returns Rejected with 100% confidence</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>fabric type + fiber composition + burn test</t>
+          <t>Donation gate</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Keep all as separate evidence sources</t>
+          <t>Uniform/institutional branding</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>When preferred pathway is Donation, uniform/company/school/institutional branding returns Rejected</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Donation uniform/branded clothing</t>
+          <t>Donation gate</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Block Donation only; store details.uniform_branding for DSS audit consistency</t>
+          <t>Heavily damaged</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>When preferred pathway is Donation, heavily damaged returns Rejected</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Fabric scraps-only Recovery Criteria</t>
+          <t>Donation gate</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Disable Wearability and Repairability; submit null values and exclude their weights from scoring</t>
+          <t>Heavily soiled/contaminated</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>When preferred pathway is Donation, heavily soiled/contaminated returns Rejected</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Donation</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Donation uniform eligibility</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>No uniforms or identifiable institutional/company/school branding</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Donation</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Good condition</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Donation</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Cleanliness</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Clean and ready for use</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Donation</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Item type</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Top, Bottoms, Outerwear</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Donation</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Fabric signal</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Cotton, linen, rayon, tencel</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Donation</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Material/fiber</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Identifiable safe textile fiber</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Donation</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Wearability</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Wearable as-is or after minor repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Donation</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Repairability</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>No repair needed or minor repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Donation</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Contamination</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Clean or washable dirt/odor</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Donation</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>No damage, minor cosmetic issue, missing button/loose seam</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Donation</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Repurposing potential</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Must not be low</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Donation</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Trim/accessory removal</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Not restrictive</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Donation</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Quantity/batch</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Any quantity</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Upcycle</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Minor damage or heavily damaged</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Upcycle</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Cleanliness</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Clean or needs cleaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Upcycle</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Item type</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Scraps, big fabric panels, or clothes</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Upcycle</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Fabric signal</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Cotton, linen, denim, wool, silk</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Upcycle</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Material/fiber</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Any clean textile with usable fabric sections</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Upcycle</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Wearability</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Not necessarily wearable, but usable fabric remains; skipped for scraps-only</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Upcycle</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Repairability</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Repair/redesign can preserve material value; skipped for scraps-only</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Upcycle</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Contamination</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Clean, washable dirt/odor, or permanent stain</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Upcycle</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Localized or structural damage with usable sections</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Upcycle</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Repurposing potential</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>High or medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Upcycle</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Trim/accessory removal</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Not many mixed components</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Upcycle</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Quantity/batch</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Any quantity</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Recycle</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Minor damage or heavily damaged</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Recycle</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Cleanliness</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Needs cleaning or heavily soiled/contaminated</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Recycle</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Item type</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Scraps or big fabric panels</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Recycle</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Fabric signal</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Polyester, poly fleece, nylon, acrylic, spandex, acetate</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Recycle</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Material/fiber</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Identifiable cotton/natural, polyester/synthetic, or accepted blend</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Recycle</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Wearability</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>No longer suitable for direct reuse; skipped for scraps-only</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Recycle</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Repairability</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Moderate repair or not practical; skipped for scraps-only</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Recycle</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Contamination</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>No chemical, mold, oil, paint, or biological contamination</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Recycle</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Damaged enough for material recovery</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Recycle</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Repurposing potential</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Low or medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Recycle</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Trim/accessory removal</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>No trims or easy-to-remove trims</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Recycle</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Quantity/batch</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Similar identifiable batch preferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Buyback preference</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Final selected pathway is Upcycle</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Ask Yes/No. If Yes, partner brief says user is open to buyback if partner supports it. If No, Upcycle only</t>
         </is>
       </c>
     </row>
